--- a/branches/dependabot/github_actions/dev/actions-e9a0a647d4/CodeSystem-mii-cs-onko-therapieabweichung.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-e9a0a647d4/CodeSystem-mii-cs-onko-therapieabweichung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T10:24:16+00:00</t>
+    <t>2026-10-20T00:05:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
